--- a/reports/relatorio_2026_03.xlsx
+++ b/reports/relatorio_2026_03.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -463,17 +463,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EDP</t>
+          <t>Claro</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R$ 0,14</t>
+          <t>R$ 227,30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,38 +483,378 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fwd: EDP - FATURAS praia</t>
+          <t>Sua Fatura Digital Claro chegou</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>downloads\pdfs\2026\BANDFATELBT01_00000000112503000471_0000000953A.pdf</t>
+          <t>downloads\pdfs\2026\Fatura Claro.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>extraido</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sua Fatura Digital Claro chegou</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\SuaContaClaro_Mar-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EDP - FATURAS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adilson Mota</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fwd: boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Adilson Mota</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fwd: boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download (3)_2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Adilson Mota</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fwd: boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download (2)_3.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Adilson Mota</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fwd: boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download (1)_4.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R$ 0,14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extraido</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fwd: EDP - FATURAS praia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\BANDFATELBT01_00000000112503000471_0000000953A.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mota, Adilson (GE Vernova)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mota, Adilson (GE Vernova)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download (3)_2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mota, Adilson (GE Vernova)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download (2)_3.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mota, Adilson (GE Vernova)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>boletos IPTU</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\download (1)_4.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CPFL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>R$ 216,16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>extraido corpo email</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Conta por e-mail CPFL - Protocolo: 0395780709</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>GRUPO KAZA JACAREÍ</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>dados incompletos</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Extrato de aluguel de locação</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>downloads\pdfs\2026\8591_0_9_5_5217939151_extrato_grupokaza.pdf</t>
         </is>
